--- a/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
+++ b/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T16:07:27+00:00</t>
+    <t>2026-08-31T20:29:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
+++ b/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:29:59+00:00</t>
+    <t>2026-09-01T08:25:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
+++ b/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:25:15+00:00</t>
+    <t>2026-09-01T09:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
+++ b/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:40:46+00:00</t>
+    <t>2026-09-01T10:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
+++ b/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T10:03:55+00:00</t>
+    <t>2026-09-01T13:17:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
+++ b/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:17:32+00:00</t>
+    <t>2026-09-03T11:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
+++ b/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="530">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:23:31+00:00</t>
+    <t>2026-09-03T16:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -896,6 +896,12 @@
   </si>
   <si>
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
+  &lt;code value="305060004"/&gt;
+&lt;/valueCoding&gt;</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -5465,7 +5471,7 @@
         <v>82</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="T29" t="s" s="2">
         <v>82</v>
@@ -5504,7 +5510,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5525,10 +5531,10 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5539,10 +5545,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5568,16 +5574,16 @@
         <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5626,7 +5632,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5647,10 +5653,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5661,10 +5667,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5687,19 +5693,19 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5748,7 +5754,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5763,19 +5769,19 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5783,10 +5789,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5809,16 +5815,16 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5868,7 +5874,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5892,10 +5898,10 @@
         <v>269</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5903,14 +5909,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5929,19 +5935,19 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5990,7 +5996,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6005,19 +6011,19 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -6025,14 +6031,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6051,19 +6057,19 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6112,7 +6118,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6127,19 +6133,19 @@
         <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6147,10 +6153,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6176,13 +6182,13 @@
         <v>129</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6232,7 +6238,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6253,13 +6259,13 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6267,10 +6273,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6293,17 +6299,17 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6352,7 +6358,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6367,19 +6373,19 @@
         <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6387,10 +6393,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6416,16 +6422,16 @@
         <v>243</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6462,17 +6468,17 @@
         <v>82</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6481,7 +6487,7 @@
         <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -6490,30 +6496,30 @@
         <v>82</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>82</v>
@@ -6538,16 +6544,16 @@
         <v>243</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6576,7 +6582,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6594,7 +6600,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6603,7 +6609,7 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>105</v>
@@ -6612,27 +6618,27 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6747,10 +6753,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6867,10 +6873,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6954,7 +6960,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6975,10 +6981,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6989,10 +6995,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7018,16 +7024,16 @@
         <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7076,7 +7082,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7097,10 +7103,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7111,10 +7117,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7140,16 +7146,16 @@
         <v>243</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7177,10 +7183,10 @@
         <v>151</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7198,7 +7204,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7207,7 +7213,7 @@
         <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>105</v>
@@ -7222,7 +7228,7 @@
         <v>192</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7233,14 +7239,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7262,16 +7268,16 @@
         <v>243</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7299,10 +7305,10 @@
         <v>151</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -7320,7 +7326,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7338,27 +7344,27 @@
         <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7381,19 +7387,19 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7442,7 +7448,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7463,10 +7469,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7477,10 +7483,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7506,13 +7512,13 @@
         <v>243</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7541,10 +7547,10 @@
         <v>159</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7562,7 +7568,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7580,27 +7586,27 @@
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7626,16 +7632,16 @@
         <v>243</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7663,10 +7669,10 @@
         <v>159</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7684,7 +7690,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7705,10 +7711,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7719,10 +7725,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7745,16 +7751,16 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7804,7 +7810,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7822,27 +7828,27 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7865,16 +7871,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7924,7 +7930,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7942,27 +7948,27 @@
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7985,19 +7991,19 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8046,7 +8052,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8058,7 +8064,7 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -8067,10 +8073,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8081,10 +8087,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8199,10 +8205,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8319,14 +8325,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8348,10 +8354,10 @@
         <v>114</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>117</v>
@@ -8406,7 +8412,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8441,10 +8447,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8467,13 +8473,13 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8524,7 +8530,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8533,7 +8539,7 @@
         <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>105</v>
@@ -8545,10 +8551,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8559,10 +8565,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8585,13 +8591,13 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8642,7 +8648,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8651,7 +8657,7 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>105</v>
@@ -8663,10 +8669,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8677,10 +8683,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8706,16 +8712,16 @@
         <v>243</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8743,10 +8749,10 @@
         <v>173</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8764,7 +8770,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8782,13 +8788,13 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8799,10 +8805,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8828,16 +8834,16 @@
         <v>243</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8865,10 +8871,10 @@
         <v>159</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8886,7 +8892,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8904,13 +8910,13 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8921,10 +8927,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8947,17 +8953,17 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9006,7 +9012,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9030,7 +9036,7 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9041,10 +9047,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9070,10 +9076,10 @@
         <v>107</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9124,7 +9130,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9145,10 +9151,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9159,10 +9165,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9185,16 +9191,16 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9244,7 +9250,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9265,10 +9271,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9279,10 +9285,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9305,16 +9311,16 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9364,7 +9370,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9385,10 +9391,10 @@
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9399,10 +9405,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9425,19 +9431,19 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9486,7 +9492,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9507,10 +9513,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9521,10 +9527,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9639,10 +9645,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9759,14 +9765,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9788,10 +9794,10 @@
         <v>114</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>117</v>
@@ -9846,7 +9852,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9881,10 +9887,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9910,13 +9916,13 @@
         <v>243</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>264</v>
@@ -9968,7 +9974,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>93</v>
@@ -9986,7 +9992,7 @@
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>269</v>
@@ -10003,10 +10009,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10029,19 +10035,19 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10090,7 +10096,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10108,27 +10114,27 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10154,16 +10160,16 @@
         <v>243</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10191,10 +10197,10 @@
         <v>151</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10212,7 +10218,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10221,7 +10227,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10236,7 +10242,7 @@
         <v>192</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10247,14 +10253,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10276,16 +10282,16 @@
         <v>243</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10313,10 +10319,10 @@
         <v>151</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10334,7 +10340,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10352,27 +10358,27 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10398,16 +10404,16 @@
         <v>82</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10456,7 +10462,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10477,10 +10483,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
+++ b/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T16:19:13+00:00</t>
+    <t>2026-09-08T13:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
+++ b/StructureDefinition-mii-pr-sdd-betreuungssituation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T13:04:20+00:00</t>
+    <t>2026-09-08T13:56:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
